--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_37.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1989871.841627037</v>
+        <v>1982089.722624709</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747597</v>
+        <v>7552736.626707198</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747597</v>
+        <v>7552736.626707198</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097731</v>
+        <v>1235723.121316086</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097731</v>
+        <v>1235723.121316086</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17696398.62559231</v>
+        <v>17761018.47209024</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +666,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>33.59582009342634</v>
       </c>
       <c r="G2" t="n">
         <v>3.75737228701621</v>
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>260.9570037095881</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>164.4576247514824</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>5.357765217513816</v>
+        <v>385</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>152.9521214909335</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>147.2737972923793</v>
+        <v>385</v>
       </c>
       <c r="S6" t="n">
-        <v>66.5639999646113</v>
+        <v>173.8479142120571</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>385</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>267.0796673663621</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>205.1757665394882</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I11" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>263.7284240682206</v>
       </c>
     </row>
     <row r="12">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H12" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,28 +1492,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U12" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V12" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1568,13 +1568,13 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>342.1496093272373</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>53.74128073011019</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1602,28 +1602,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>185.3828212651317</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H15" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U15" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V15" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1790,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>139.1349830766932</v>
       </c>
       <c r="O16" t="n">
-        <v>143.6019811694581</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1839,28 +1839,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>184.2505648441361</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T17" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H18" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,28 +1966,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S18" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U18" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V18" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>237.2236891051136</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2076,28 +2076,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>188.5028512606473</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,28 +2124,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T20" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U20" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V20" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H21" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,28 +2203,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U21" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V21" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>46.51799792468744</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>56.01884949035202</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2313,28 +2313,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>5.493192557119869</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,28 +2361,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T23" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U23" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V23" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="24">
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H24" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,28 +2440,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U24" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V24" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>224.4127176976028</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>262.4925055126944</v>
       </c>
       <c r="C26" t="n">
         <v>224.4745782429939</v>
@@ -2571,7 +2571,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>46.32480308512611</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2735,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>34.81182523486971</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>291.3939435207857</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2802,7 +2802,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>184.2505648441361</v>
       </c>
       <c r="H29" t="n">
         <v>183.0096587035274</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
         <v>269.8481678023229</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>99.6478606230321</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>367.2818334606677</v>
+        <v>372.7750260177875</v>
       </c>
       <c r="Y32" t="n">
         <v>286.3174326828064</v>
@@ -3191,10 +3191,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F34" t="n">
-        <v>45.14518808597774</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>284.7958946515711</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3400,13 +3400,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>121.4947832967418</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3586,13 +3586,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>152.3788082133584</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>121.4947832967418</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>11.09991244551929</v>
+        <v>98.0381390959345</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4111,16 +4111,16 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169627</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4309,13 +4309,13 @@
         <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4327,19 +4327,19 @@
         <v>411.95</v>
       </c>
       <c r="L2" t="n">
-        <v>411.95</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>1158.85</v>
       </c>
       <c r="N2" t="n">
-        <v>793.1</v>
+        <v>1540</v>
       </c>
       <c r="O2" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="P2" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="C3" t="n">
-        <v>532.4421332706097</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>532.4421332706097</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>532.4421332706097</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>532.4421332706097</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>366.3233203903244</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4430,22 +4430,22 @@
         <v>970.2346453614745</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>581.3457564725855</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>581.1332718663363</v>
       </c>
       <c r="V3" t="n">
-        <v>949.9530371097363</v>
+        <v>566.4760322789422</v>
       </c>
       <c r="W3" t="n">
-        <v>917.2528927563742</v>
+        <v>533.77588792558</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>513.7125147484209</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1058.488973253216</v>
+        <v>826.3619486073318</v>
       </c>
       <c r="C4" t="n">
-        <v>1184.490979071652</v>
+        <v>826.3619486073318</v>
       </c>
       <c r="D4" t="n">
-        <v>1297.810123196652</v>
+        <v>826.3619486073318</v>
       </c>
       <c r="E4" t="n">
-        <v>1415.639027408065</v>
+        <v>944.1908528187448</v>
       </c>
       <c r="F4" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="G4" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="H4" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="I4" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4506,25 +4506,25 @@
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>68.05025509417312</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>313.5792327380745</v>
+        <v>344.2403367826761</v>
       </c>
       <c r="V4" t="n">
-        <v>512.4006256240204</v>
+        <v>543.0617296686221</v>
       </c>
       <c r="W4" t="n">
-        <v>684.2915438836978</v>
+        <v>714.9526479282995</v>
       </c>
       <c r="X4" t="n">
-        <v>835.3223349078913</v>
+        <v>714.9526479282995</v>
       </c>
       <c r="Y4" t="n">
-        <v>946.7316355869236</v>
+        <v>826.3619486073318</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
@@ -4567,43 +4567,43 @@
         <v>411.9499999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>793.0999999999999</v>
+        <v>793.1000000000035</v>
       </c>
       <c r="N5" t="n">
-        <v>1158.85</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="O5" t="n">
-        <v>1158.85</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="P5" t="n">
-        <v>1158.85</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
       </c>
       <c r="R5" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>528.3640038674853</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="C6" t="n">
-        <v>528.3640038674853</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="D6" t="n">
         <v>373.8669114524009</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1037.471008962092</v>
+        <v>622.5159909842129</v>
       </c>
       <c r="S6" t="n">
-        <v>970.2346453614745</v>
+        <v>446.9120372346603</v>
       </c>
       <c r="T6" t="n">
-        <v>964.8227613033797</v>
+        <v>441.5001531765655</v>
       </c>
       <c r="U6" t="n">
-        <v>964.6102766971304</v>
+        <v>441.2876685703163</v>
       </c>
       <c r="V6" t="n">
-        <v>949.9530371097363</v>
+        <v>426.6304289829222</v>
       </c>
       <c r="W6" t="n">
-        <v>917.2528927563742</v>
+        <v>393.93028462956</v>
       </c>
       <c r="X6" t="n">
-        <v>528.3640038674853</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="Y6" t="n">
-        <v>528.3640038674853</v>
+        <v>373.8669114524009</v>
       </c>
     </row>
     <row r="7">
@@ -4692,22 +4692,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>425.8575566050018</v>
+        <v>341.0306935649782</v>
       </c>
       <c r="C7" t="n">
-        <v>425.8575566050018</v>
+        <v>467.032699383414</v>
       </c>
       <c r="D7" t="n">
-        <v>539.1767007300019</v>
+        <v>467.032699383414</v>
       </c>
       <c r="E7" t="n">
-        <v>553.5413887232644</v>
+        <v>467.032699383414</v>
       </c>
       <c r="F7" t="n">
-        <v>677.9023613151999</v>
+        <v>591.3936719753494</v>
       </c>
       <c r="G7" t="n">
-        <v>677.9023613151999</v>
+        <v>744.8002378622347</v>
       </c>
       <c r="H7" t="n">
         <v>847.4189464745974</v>
@@ -4752,16 +4752,16 @@
         <v>30.8</v>
       </c>
       <c r="V7" t="n">
-        <v>30.8</v>
+        <v>229.621392885946</v>
       </c>
       <c r="W7" t="n">
-        <v>202.6909182596774</v>
+        <v>229.621392885946</v>
       </c>
       <c r="X7" t="n">
-        <v>202.6909182596774</v>
+        <v>229.621392885946</v>
       </c>
       <c r="Y7" t="n">
-        <v>314.1002189387097</v>
+        <v>341.0306935649782</v>
       </c>
     </row>
     <row r="8">
@@ -4771,37 +4771,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G8" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="K8" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="L8" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="M8" t="n">
         <v>777.6999999999999</v>
@@ -4834,13 +4834,13 @@
         <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4904,22 +4904,22 @@
         <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>762.9863963316884</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>762.7739117254391</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>748.116672138045</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>715.4165277846829</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>695.3531546075237</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>695.3531546075237</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>823.439540267482</v>
+        <v>888.972388093818</v>
       </c>
       <c r="C10" t="n">
-        <v>823.439540267482</v>
+        <v>1014.974393912254</v>
       </c>
       <c r="D10" t="n">
-        <v>936.7586843924821</v>
+        <v>1128.293538037254</v>
       </c>
       <c r="E10" t="n">
-        <v>1054.587588603895</v>
+        <v>1246.122442248667</v>
       </c>
       <c r="F10" t="n">
-        <v>1165.460555177032</v>
+        <v>1370.483414840602</v>
       </c>
       <c r="G10" t="n">
-        <v>1318.867121063917</v>
+        <v>1370.483414840602</v>
       </c>
       <c r="H10" t="n">
-        <v>1318.867121063917</v>
+        <v>1540</v>
       </c>
       <c r="I10" t="n">
         <v>1540</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>277.3511926382866</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>277.3511926382866</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="W10" t="n">
-        <v>449.242110897964</v>
+        <v>626.1842594033325</v>
       </c>
       <c r="X10" t="n">
-        <v>600.2729019221575</v>
+        <v>777.215050427526</v>
       </c>
       <c r="Y10" t="n">
-        <v>711.6822026011898</v>
+        <v>777.215050427526</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1229.164925096351</v>
+        <v>1057.960488169967</v>
       </c>
       <c r="C11" t="n">
-        <v>1002.422926871105</v>
+        <v>857.4811162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>815.2116584470142</v>
+        <v>696.532474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>634.0366184400762</v>
+        <v>541.6200603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>452.3299227754177</v>
+        <v>386.175990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>271.7669204653003</v>
+        <v>231.8756148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>86.90867935062613</v>
+        <v>73.28</v>
       </c>
       <c r="I11" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J11" t="n">
-        <v>374.1524465568547</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1083.858812904723</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1990.888307474345</v>
+        <v>2081.135479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2501.73713620328</v>
+        <v>2081.135479385524</v>
       </c>
       <c r="N11" t="n">
-        <v>3114.957455978044</v>
+        <v>2081.135479385524</v>
       </c>
       <c r="O11" t="n">
-        <v>4068</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="P11" t="n">
-        <v>4068</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q11" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R11" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S11" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X11" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y11" t="n">
-        <v>1488.760190708043</v>
+        <v>1291.293127519033</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C12" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D12" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E12" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F12" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G12" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H12" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>230.7713981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>847.8042142372474</v>
+        <v>419.9642142372473</v>
       </c>
       <c r="L12" t="n">
-        <v>1341.904675832448</v>
+        <v>939.8046758324475</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.735217575307</v>
+        <v>1025.885217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>2006.765502182875</v>
+        <v>1407.655502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2468.557953866594</v>
+        <v>1895.187953866594</v>
       </c>
       <c r="P12" t="n">
-        <v>2651.414528442776</v>
+        <v>2172.253606942957</v>
       </c>
       <c r="Q12" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R12" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S12" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T12" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U12" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V12" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W12" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X12" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y12" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G13" t="n">
-        <v>195.0582646830375</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H13" t="n">
-        <v>191.2490463985742</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I13" t="n">
-        <v>239.1319253346571</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="N13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="O13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="P13" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="Q13" t="n">
-        <v>81.36</v>
+        <v>127.5641219496063</v>
       </c>
       <c r="R13" t="n">
-        <v>81.36</v>
+        <v>127.5641219496063</v>
       </c>
       <c r="S13" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T13" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>195.0582646830375</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C14" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D14" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E14" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F14" t="n">
-        <v>446.7812434247916</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G14" t="n">
-        <v>266.2182411146742</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H14" t="n">
-        <v>81.36</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I14" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J14" t="n">
-        <v>472.6691130376557</v>
+        <v>73.28</v>
       </c>
       <c r="K14" t="n">
-        <v>1182.375479385524</v>
+        <v>771.5028875891945</v>
       </c>
       <c r="L14" t="n">
-        <v>1552.289212421678</v>
+        <v>771.5028875891945</v>
       </c>
       <c r="M14" t="n">
-        <v>2063.138041150613</v>
+        <v>1282.35171631813</v>
       </c>
       <c r="N14" t="n">
-        <v>2676.358360925376</v>
+        <v>1895.572036092893</v>
       </c>
       <c r="O14" t="n">
-        <v>3629.400904947332</v>
+        <v>2802.412036092893</v>
       </c>
       <c r="P14" t="n">
-        <v>3629.400904947332</v>
+        <v>3664</v>
       </c>
       <c r="Q14" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R14" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S14" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y14" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C15" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D15" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E15" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F15" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G15" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H15" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I15" t="n">
-        <v>89.15487796756496</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J15" t="n">
-        <v>283.4386282495398</v>
+        <v>230.7713981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>695.3814443439232</v>
+        <v>668.4542142372472</v>
       </c>
       <c r="L15" t="n">
-        <v>1189.481905939123</v>
+        <v>939.8046758324474</v>
       </c>
       <c r="M15" t="n">
-        <v>1498.312447681983</v>
+        <v>1274.375217575307</v>
       </c>
       <c r="N15" t="n">
-        <v>1854.342732289551</v>
+        <v>1649.333338350157</v>
       </c>
       <c r="O15" t="n">
-        <v>2316.13518397327</v>
+        <v>2136.865790033876</v>
       </c>
       <c r="P15" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q15" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R15" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S15" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T15" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U15" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V15" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W15" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X15" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y15" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G16" t="n">
-        <v>195.0582646830375</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H16" t="n">
-        <v>191.2490463985742</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I16" t="n">
-        <v>239.1319253346571</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J16" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K16" t="n">
-        <v>426.9656659871084</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L16" t="n">
-        <v>226.4125062317759</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M16" t="n">
-        <v>226.4125062317759</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="N16" t="n">
-        <v>226.4125062317759</v>
+        <v>466.6593576555707</v>
       </c>
       <c r="O16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="P16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="R16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T16" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W16" t="n">
-        <v>195.0582646830375</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D17" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E17" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F17" t="n">
-        <v>452.3299227754177</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G17" t="n">
-        <v>266.2182411146742</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H17" t="n">
-        <v>81.36</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I17" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J17" t="n">
-        <v>472.6691130376557</v>
+        <v>73.28</v>
       </c>
       <c r="K17" t="n">
-        <v>1182.375479385524</v>
+        <v>782.9863663478684</v>
       </c>
       <c r="L17" t="n">
-        <v>1182.375479385524</v>
+        <v>1194.491756443634</v>
       </c>
       <c r="M17" t="n">
-        <v>1693.224308114459</v>
+        <v>1705.340585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>2306.444627889222</v>
+        <v>2318.560904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>3259.487171911179</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q17" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R17" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S17" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X17" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y17" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C18" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D18" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E18" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F18" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G18" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H18" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I18" t="n">
-        <v>89.15487796756496</v>
+        <v>73.28</v>
       </c>
       <c r="J18" t="n">
-        <v>435.8613981428639</v>
+        <v>223.9592343101459</v>
       </c>
       <c r="K18" t="n">
-        <v>847.8042142372474</v>
+        <v>413.1520504045293</v>
       </c>
       <c r="L18" t="n">
-        <v>1138.080378378698</v>
+        <v>684.5025119997294</v>
       </c>
       <c r="M18" t="n">
-        <v>1446.910920121557</v>
+        <v>1019.073053742589</v>
       </c>
       <c r="N18" t="n">
-        <v>1802.941204729126</v>
+        <v>1400.843338350157</v>
       </c>
       <c r="O18" t="n">
-        <v>2264.733656412845</v>
+        <v>1888.375790033876</v>
       </c>
       <c r="P18" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q18" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R18" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S18" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T18" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U18" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V18" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W18" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X18" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y18" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C19" t="n">
-        <v>195.0582646830375</v>
+        <v>270.1552803830249</v>
       </c>
       <c r="D19" t="n">
-        <v>195.0582646830375</v>
+        <v>270.1552803830249</v>
       </c>
       <c r="E19" t="n">
-        <v>195.0582646830375</v>
+        <v>270.1552803830249</v>
       </c>
       <c r="F19" t="n">
-        <v>195.0582646830375</v>
+        <v>270.1552803830249</v>
       </c>
       <c r="G19" t="n">
-        <v>195.0582646830375</v>
+        <v>276.0518462699101</v>
       </c>
       <c r="H19" t="n">
-        <v>195.0582646830375</v>
+        <v>298.0584314293077</v>
       </c>
       <c r="I19" t="n">
-        <v>242.9411436191204</v>
+        <v>371.6813103653906</v>
       </c>
       <c r="J19" t="n">
-        <v>430.7748842715717</v>
+        <v>585.2550510178419</v>
       </c>
       <c r="K19" t="n">
-        <v>430.7748842715717</v>
+        <v>585.2550510178419</v>
       </c>
       <c r="L19" t="n">
-        <v>430.7748842715717</v>
+        <v>585.2550510178419</v>
       </c>
       <c r="M19" t="n">
-        <v>430.7748842715717</v>
+        <v>312.8998879849632</v>
       </c>
       <c r="N19" t="n">
-        <v>430.7748842715717</v>
+        <v>312.8998879849632</v>
       </c>
       <c r="O19" t="n">
-        <v>430.7748842715717</v>
+        <v>312.8998879849632</v>
       </c>
       <c r="P19" t="n">
-        <v>430.7748842715717</v>
+        <v>73.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>430.7748842715717</v>
+        <v>73.28</v>
       </c>
       <c r="R19" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S19" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T19" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>195.0582646830375</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C20" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D20" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E20" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F20" t="n">
-        <v>452.3299227754177</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G20" t="n">
-        <v>271.7669204653003</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H20" t="n">
-        <v>81.36</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I20" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J20" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1182.375479385524</v>
+        <v>988.7320360928928</v>
       </c>
       <c r="L20" t="n">
-        <v>2089.404973955146</v>
+        <v>1895.572036092893</v>
       </c>
       <c r="M20" t="n">
-        <v>2600.253802684082</v>
+        <v>1895.572036092893</v>
       </c>
       <c r="N20" t="n">
-        <v>3213.474122458845</v>
+        <v>1895.572036092893</v>
       </c>
       <c r="O20" t="n">
-        <v>3629.400904947332</v>
+        <v>2802.412036092893</v>
       </c>
       <c r="P20" t="n">
-        <v>3629.400904947332</v>
+        <v>3664</v>
       </c>
       <c r="Q20" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R20" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S20" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X20" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y20" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2204.262200814254</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C21" t="n">
-        <v>2066.787541778376</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D21" t="n">
-        <v>1942.608060063525</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E21" t="n">
-        <v>1823.747355798966</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F21" t="n">
-        <v>1707.953171619293</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G21" t="n">
-        <v>1606.196064674821</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H21" t="n">
-        <v>1497.945471557224</v>
+        <v>73.28</v>
       </c>
       <c r="I21" t="n">
-        <v>1497.945471557224</v>
+        <v>73.28</v>
       </c>
       <c r="J21" t="n">
-        <v>1844.651991732522</v>
+        <v>445.7265201752989</v>
       </c>
       <c r="K21" t="n">
-        <v>2256.594807826906</v>
+        <v>883.4093362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>2750.695269422106</v>
+        <v>1154.759797864882</v>
       </c>
       <c r="M21" t="n">
-        <v>3059.525811164965</v>
+        <v>1489.330339607742</v>
       </c>
       <c r="N21" t="n">
-        <v>3415.556095772533</v>
+        <v>1622.61062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>3681.319127970068</v>
+        <v>2110.143075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>4016.598472439575</v>
+        <v>2222.672420368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>4068</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R21" t="n">
-        <v>3742.470911825879</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S21" t="n">
-        <v>3498.466871457585</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T21" t="n">
-        <v>3316.287310631813</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U21" t="n">
-        <v>3139.307149257887</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V21" t="n">
-        <v>2947.882232902817</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W21" t="n">
-        <v>2738.414411781778</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X21" t="n">
-        <v>2541.583361836942</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y21" t="n">
-        <v>2365.430439850948</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195.0582646830375</v>
+        <v>255.6213877678391</v>
       </c>
       <c r="C22" t="n">
-        <v>195.0582646830375</v>
+        <v>255.6213877678391</v>
       </c>
       <c r="D22" t="n">
-        <v>195.0582646830375</v>
+        <v>255.6213877678391</v>
       </c>
       <c r="E22" t="n">
-        <v>148.070387991434</v>
+        <v>255.6213877678391</v>
       </c>
       <c r="F22" t="n">
-        <v>148.070387991434</v>
+        <v>255.6213877678391</v>
       </c>
       <c r="G22" t="n">
-        <v>148.070387991434</v>
+        <v>261.5179536547243</v>
       </c>
       <c r="H22" t="n">
-        <v>144.2611697069707</v>
+        <v>283.5245388141219</v>
       </c>
       <c r="I22" t="n">
-        <v>192.1440486430537</v>
+        <v>357.1474177502048</v>
       </c>
       <c r="J22" t="n">
-        <v>379.977789295505</v>
+        <v>570.7211584026561</v>
       </c>
       <c r="K22" t="n">
-        <v>379.977789295505</v>
+        <v>570.7211584026561</v>
       </c>
       <c r="L22" t="n">
-        <v>379.977789295505</v>
+        <v>570.7211584026561</v>
       </c>
       <c r="M22" t="n">
-        <v>81.36</v>
+        <v>570.7211584026561</v>
       </c>
       <c r="N22" t="n">
-        <v>81.36</v>
+        <v>570.7211584026561</v>
       </c>
       <c r="O22" t="n">
-        <v>81.36</v>
+        <v>570.7211584026561</v>
       </c>
       <c r="P22" t="n">
-        <v>81.36</v>
+        <v>129.864696454901</v>
       </c>
       <c r="Q22" t="n">
-        <v>81.36</v>
+        <v>129.864696454901</v>
       </c>
       <c r="R22" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S22" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T22" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U22" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V22" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>195.0582646830375</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C23" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D23" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E23" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F23" t="n">
-        <v>452.3299227754177</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G23" t="n">
-        <v>271.7669204653003</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H23" t="n">
-        <v>86.90867935062613</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I23" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J23" t="n">
-        <v>294.5205826738834</v>
+        <v>73.28</v>
       </c>
       <c r="K23" t="n">
-        <v>294.5205826738834</v>
+        <v>73.28</v>
       </c>
       <c r="L23" t="n">
-        <v>1201.550077243506</v>
+        <v>980.12</v>
       </c>
       <c r="M23" t="n">
-        <v>1201.550077243506</v>
+        <v>1490.968828728935</v>
       </c>
       <c r="N23" t="n">
-        <v>1814.770397018269</v>
+        <v>2104.189148503698</v>
       </c>
       <c r="O23" t="n">
-        <v>2767.812941040225</v>
+        <v>3011.029148503698</v>
       </c>
       <c r="P23" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q23" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R23" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S23" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X23" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y23" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C24" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D24" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E24" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F24" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G24" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H24" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I24" t="n">
-        <v>89.15487796756496</v>
+        <v>73.28</v>
       </c>
       <c r="J24" t="n">
-        <v>435.8613981428639</v>
+        <v>445.7265201752989</v>
       </c>
       <c r="K24" t="n">
-        <v>643.9799167834981</v>
+        <v>634.9193362696823</v>
       </c>
       <c r="L24" t="n">
-        <v>1138.080378378698</v>
+        <v>906.2697978648823</v>
       </c>
       <c r="M24" t="n">
-        <v>1446.910920121557</v>
+        <v>1240.840339607741</v>
       </c>
       <c r="N24" t="n">
-        <v>1802.941204729126</v>
+        <v>1400.843338350157</v>
       </c>
       <c r="O24" t="n">
-        <v>2264.733656412845</v>
+        <v>1888.375790033876</v>
       </c>
       <c r="P24" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q24" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R24" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S24" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T24" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U24" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V24" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W24" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X24" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y24" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C25" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D25" t="n">
-        <v>195.0582646830375</v>
+        <v>257.2149052239231</v>
       </c>
       <c r="E25" t="n">
-        <v>195.0582646830375</v>
+        <v>257.2149052239231</v>
       </c>
       <c r="F25" t="n">
-        <v>195.0582646830375</v>
+        <v>257.2149052239231</v>
       </c>
       <c r="G25" t="n">
-        <v>195.0582646830375</v>
+        <v>263.1114711108083</v>
       </c>
       <c r="H25" t="n">
-        <v>191.2490463985742</v>
+        <v>285.1180562702059</v>
       </c>
       <c r="I25" t="n">
-        <v>239.1319253346571</v>
+        <v>358.7409352062888</v>
       </c>
       <c r="J25" t="n">
-        <v>426.9656659871084</v>
+        <v>572.3146758587401</v>
       </c>
       <c r="K25" t="n">
-        <v>426.9656659871084</v>
+        <v>572.3146758587401</v>
       </c>
       <c r="L25" t="n">
-        <v>426.9656659871084</v>
+        <v>572.3146758587401</v>
       </c>
       <c r="M25" t="n">
-        <v>426.9656659871084</v>
+        <v>299.9595128258614</v>
       </c>
       <c r="N25" t="n">
-        <v>426.9656659871084</v>
+        <v>73.28</v>
       </c>
       <c r="O25" t="n">
-        <v>426.9656659871084</v>
+        <v>73.28</v>
       </c>
       <c r="P25" t="n">
-        <v>426.9656659871084</v>
+        <v>73.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="R25" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S25" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T25" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>195.0582646830375</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="26">
@@ -6193,46 +6193,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C26" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D26" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E26" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F26" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G26" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H26" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I26" t="n">
         <v>81.36</v>
       </c>
       <c r="J26" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>791.0663663478683</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1698.095860917491</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>2208.944689646426</v>
+        <v>1693.224308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>2822.165009421189</v>
+        <v>2306.444627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P26" t="n">
         <v>3629.400904947332</v>
@@ -6308,13 +6308,13 @@
         <v>1642.940339607742</v>
       </c>
       <c r="N27" t="n">
-        <v>1998.97062421531</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O27" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P27" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q27" t="n">
         <v>2651.414528442776</v>
@@ -6351,49 +6351,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>131.9619486734795</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>131.9619486734795</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>131.9619486734795</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>131.9619486734795</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>85.16921828446326</v>
+        <v>143.7899153835914</v>
       </c>
       <c r="G28" t="n">
-        <v>85.16921828446326</v>
+        <v>143.7899153835914</v>
       </c>
       <c r="H28" t="n">
-        <v>81.36</v>
+        <v>139.9806970991281</v>
       </c>
       <c r="I28" t="n">
-        <v>129.2428789360829</v>
+        <v>187.863576035211</v>
       </c>
       <c r="J28" t="n">
-        <v>317.0766195885342</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="K28" t="n">
-        <v>281.9131597553325</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="L28" t="n">
-        <v>81.36</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="M28" t="n">
-        <v>81.36</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="N28" t="n">
-        <v>81.36</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="O28" t="n">
-        <v>81.36</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="P28" t="n">
-        <v>81.36</v>
+        <v>375.6973166876624</v>
       </c>
       <c r="Q28" t="n">
         <v>81.36</v>
@@ -6414,13 +6414,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>131.9619486734795</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C29" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D29" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E29" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F29" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G29" t="n">
         <v>266.2182411146742</v>
@@ -6454,52 +6454,52 @@
         <v>81.36</v>
       </c>
       <c r="J29" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>791.0663663478683</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>1698.095860917491</v>
+        <v>1379.698607607278</v>
       </c>
       <c r="M29" t="n">
-        <v>2208.944689646426</v>
+        <v>1890.547436336213</v>
       </c>
       <c r="N29" t="n">
-        <v>2253.369492070936</v>
+        <v>2503.767756110976</v>
       </c>
       <c r="O29" t="n">
-        <v>3206.412036092893</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P29" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>4068</v>
       </c>
       <c r="R29" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W29" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X29" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y29" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="30">
@@ -6533,10 +6533,10 @@
         <v>81.36</v>
       </c>
       <c r="J30" t="n">
-        <v>428.066520175299</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K30" t="n">
-        <v>840.0093362696824</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L30" t="n">
         <v>1138.080378378698</v>
@@ -6591,43 +6591,43 @@
         <v>195.0582646830375</v>
       </c>
       <c r="C31" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="D31" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="E31" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="F31" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="G31" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="H31" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="I31" t="n">
-        <v>242.9411436191204</v>
+        <v>194.7338237726106</v>
       </c>
       <c r="J31" t="n">
-        <v>430.7748842715717</v>
+        <v>382.5675644250619</v>
       </c>
       <c r="K31" t="n">
-        <v>430.7748842715717</v>
+        <v>382.5675644250619</v>
       </c>
       <c r="L31" t="n">
-        <v>430.7748842715717</v>
+        <v>182.0144046697294</v>
       </c>
       <c r="M31" t="n">
-        <v>430.7748842715717</v>
+        <v>182.0144046697294</v>
       </c>
       <c r="N31" t="n">
-        <v>430.7748842715717</v>
+        <v>182.0144046697294</v>
       </c>
       <c r="O31" t="n">
-        <v>81.36</v>
+        <v>182.0144046697294</v>
       </c>
       <c r="P31" t="n">
         <v>81.36</v>
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C32" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D32" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E32" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F32" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G32" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H32" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I32" t="n">
         <v>81.36</v>
       </c>
       <c r="J32" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K32" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L32" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="M32" t="n">
-        <v>1693.224308114459</v>
+        <v>1301.915195076803</v>
       </c>
       <c r="N32" t="n">
-        <v>2306.444627889222</v>
+        <v>1915.135514851567</v>
       </c>
       <c r="O32" t="n">
-        <v>3259.487171911179</v>
+        <v>2868.178058873523</v>
       </c>
       <c r="P32" t="n">
-        <v>4068</v>
+        <v>3729.766022780631</v>
       </c>
       <c r="Q32" t="n">
         <v>4068</v>
@@ -6733,10 +6733,10 @@
         <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y32" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="33">
@@ -6767,16 +6767,16 @@
         <v>81.36</v>
       </c>
       <c r="I33" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>428.066520175299</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L33" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M33" t="n">
         <v>1446.910920121557</v>
@@ -6834,43 +6834,43 @@
         <v>193.6715880782802</v>
       </c>
       <c r="E34" t="n">
-        <v>193.6715880782802</v>
+        <v>137.1252195561019</v>
       </c>
       <c r="F34" t="n">
-        <v>148.070387991434</v>
+        <v>137.1252195561019</v>
       </c>
       <c r="G34" t="n">
-        <v>148.070387991434</v>
+        <v>137.1252195561019</v>
       </c>
       <c r="H34" t="n">
-        <v>144.2611697069707</v>
+        <v>133.3160012716386</v>
       </c>
       <c r="I34" t="n">
-        <v>192.1440486430537</v>
+        <v>181.1988802077215</v>
       </c>
       <c r="J34" t="n">
-        <v>379.977789295505</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="K34" t="n">
-        <v>379.977789295505</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="L34" t="n">
-        <v>379.977789295505</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="M34" t="n">
-        <v>81.36</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="N34" t="n">
-        <v>81.36</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="O34" t="n">
-        <v>81.36</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="P34" t="n">
-        <v>81.36</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="Q34" t="n">
-        <v>81.36</v>
+        <v>369.0326208601729</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6937,16 +6937,16 @@
         <v>1151.54</v>
       </c>
       <c r="M35" t="n">
-        <v>1151.54</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N35" t="n">
-        <v>1704.95</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O35" t="n">
-        <v>1704.95</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7043,16 +7043,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>274.6072361907175</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="37">
@@ -7062,22 +7062,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
         <v>1377.480007433093</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7165,13 +7165,13 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>179.7320762183976</v>
+        <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>733.1420762183976</v>
+        <v>598.13</v>
       </c>
       <c r="L38" t="n">
-        <v>733.1420762183976</v>
+        <v>1151.54</v>
       </c>
       <c r="M38" t="n">
         <v>1243.990904947333</v>
@@ -7180,7 +7180,7 @@
         <v>1243.990904947333</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>402.0654643105373</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C39" t="n">
-        <v>390.8534315372855</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D39" t="n">
-        <v>390.8534315372855</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G39" t="n">
         <v>44.72</v>
@@ -7283,13 +7283,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>557.4297964901822</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>486.8613728079725</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>436.9710770846045</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="40">
@@ -7405,22 +7405,22 @@
         <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>44.72</v>
+        <v>598.13</v>
       </c>
       <c r="L41" t="n">
-        <v>598.13</v>
+        <v>1151.54</v>
       </c>
       <c r="M41" t="n">
-        <v>1108.978828728935</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.9618669904511</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
         <v>373.7498342171993</v>
@@ -7615,49 +7615,49 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>64.92117127106526</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>64.92117127106526</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>618.3311712710653</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>1129.18</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N44" t="n">
-        <v>1682.59</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7754,16 +7754,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>444.3729990826727</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7970,22 +7970,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>862.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>542.2671287719298</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>929.2621276423208</v>
       </c>
       <c r="N5" t="n">
-        <v>846.6934025142797</v>
+        <v>862.2489580698386</v>
       </c>
       <c r="O5" t="n">
         <v>70.24786957409245</v>
@@ -8222,7 +8222,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.8226843274854</v>
+        <v>542.267128771923</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>404.4874506895348</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N8" t="n">
         <v>862.2489580698352</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>330.7929522621153</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>1032.917105959907</v>
+        <v>355.7806591242959</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>705.2756440294895</v>
       </c>
       <c r="L14" t="n">
-        <v>373.6502353900541</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>1032.917105959907</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>415.6620101977433</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,10 +9164,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>1032.917105959907</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>373.9372954307356</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9389,25 +9389,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>529.437296015391</v>
       </c>
       <c r="L20" t="n">
-        <v>916.1914086561842</v>
+        <v>916</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>490.3759326937771</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>250.3567261176999</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>916</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>1032.917105959907</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>870.5779326741233</v>
+        <v>216.8241877615241</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>885.6376630348439</v>
+        <v>536.2764687165196</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>916.1914086561842</v>
@@ -10109,16 +10109,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>522.1224958723714</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>1032.917105959907</v>
+        <v>336.9601775834349</v>
       </c>
       <c r="P29" t="n">
         <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
@@ -10352,10 +10352,10 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P32" t="n">
-        <v>816.9666843728241</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>514.4731663672521</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,19 +10580,19 @@
         <v>559.0000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>206.6237041381302</v>
       </c>
       <c r="P35" t="n">
-        <v>536.7012014548227</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>171.4188408091283</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>637.6468801143703</v>
       </c>
       <c r="N38" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,25 +11048,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O41" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>55.44822975121687</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>257.410082171668</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23381,22 +23381,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -23408,31 +23408,31 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M13" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>158.6896570983607</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>57.63219897274524</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23444,13 +23444,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -23618,22 +23618,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,31 +23645,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>346.1850752716849</v>
+        <v>181.0500921949917</v>
       </c>
       <c r="O16" t="n">
-        <v>271.8435829095568</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>500.839266425598</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23681,13 +23681,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23855,25 +23855,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F19" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G19" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23882,31 +23882,31 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L19" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>462.4478973282775</v>
+        <v>199.2242082231639</v>
       </c>
       <c r="Q19" t="n">
-        <v>500.839266425598</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>155.6813925522951</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23918,13 +23918,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -24092,22 +24092,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D22" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>9.462906912269098</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F22" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G22" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -24119,31 +24119,31 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L22" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>462.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>500.839266425598</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>501.6021279811511</v>
+        <v>419.583278490799</v>
       </c>
       <c r="S22" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24155,13 +24155,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -24329,22 +24329,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C25" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F25" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G25" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -24356,31 +24356,31 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L25" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>346.1850752716849</v>
+        <v>95.77235757408215</v>
       </c>
       <c r="O25" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>158.6896570983607</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24392,13 +24392,13 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -24578,7 +24578,7 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>3.058052882615812</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>20.04387284153003</v>
@@ -24593,10 +24593,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>28.70894856627333</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>295.6316114025499</v>
@@ -24611,7 +24611,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>500.839266425598</v>
+        <v>209.4453229048123</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
@@ -24629,13 +24629,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24806,7 +24806,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>60.53621805555548</v>
@@ -24833,7 +24833,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>295.6316114025499</v>
@@ -24842,10 +24842,10 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>69.52482865015901</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>462.4478973282775</v>
+        <v>362.8000367052454</v>
       </c>
       <c r="Q31" t="n">
         <v>500.839266425598</v>
@@ -25049,10 +25049,10 @@
         <v>60.53621805555548</v>
       </c>
       <c r="E34" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4.237667881764189</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G34" t="n">
         <v>20.04387284153003</v>
@@ -25073,7 +25073,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>346.1850752716849</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>501.6021279811511</v>
+        <v>216.8062333295799</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4182269.175270727</v>
+        <v>4189775.907184801</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5162617.364816884</v>
+        <v>5182405.863796546</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6142965.554363038</v>
+        <v>6175035.820408288</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7123313.743909189</v>
+        <v>7167665.777020028</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8103661.933455341</v>
+        <v>8160295.733631767</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9084010.123001495</v>
+        <v>9145418.958329435</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10064358.31254765</v>
+        <v>10125767.14787559</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11044706.5020938</v>
+        <v>11106115.33742174</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12062039.43067122</v>
+        <v>12123448.26599917</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13101025.48894562</v>
+        <v>13162434.32427356</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14140011.54722002</v>
+        <v>14201420.38254796</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15178997.60549442</v>
+        <v>15240406.44082236</v>
       </c>
     </row>
   </sheetData>
@@ -26272,31 +26272,31 @@
         <v>1164888.438319308</v>
       </c>
       <c r="C2" t="n">
-        <v>1164888.438319308</v>
+        <v>1164888.438319307</v>
       </c>
       <c r="D2" t="n">
         <v>1164888.438319308</v>
       </c>
       <c r="E2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="F2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="G2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="H2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="I2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.73923135</v>
       </c>
       <c r="J2" t="n">
         <v>1099178.273127508</v>
       </c>
       <c r="K2" t="n">
-        <v>1099178.273127509</v>
+        <v>1099178.273127508</v>
       </c>
       <c r="L2" t="n">
         <v>1099178.273127508</v>
@@ -26305,10 +26305,10 @@
         <v>1164923.76230765</v>
       </c>
       <c r="N2" t="n">
+        <v>1164923.762307649</v>
+      </c>
+      <c r="O2" t="n">
         <v>1164923.76230765</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1164923.762307649</v>
       </c>
       <c r="P2" t="n">
         <v>1164923.762307649</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>402464</v>
+        <v>387712</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>315520</v>
+        <v>351072</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>161248</v>
+        <v>125696</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>468964.8457662077</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>467405.5293950558</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>465844.0612258157</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>464280.4258278603</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608351</v>
+        <v>462714.60756951</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203551</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26434,19 +26434,19 @@
         <v>57035.6</v>
       </c>
       <c r="E5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="F5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="H5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="I5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="J5" t="n">
         <v>80749.125</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>401418.7134197986</v>
+        <v>399902.8577314826</v>
       </c>
       <c r="C6" t="n">
-        <v>538996.6935536127</v>
+        <v>537480.8378652966</v>
       </c>
       <c r="D6" t="n">
-        <v>541057.4654659288</v>
+        <v>539541.6097776132</v>
       </c>
       <c r="E6" t="n">
-        <v>170112.4586156462</v>
+        <v>179477.7744651418</v>
       </c>
       <c r="F6" t="n">
-        <v>574030.0093792764</v>
+        <v>568749.0908362936</v>
       </c>
       <c r="G6" t="n">
-        <v>575485.5659884247</v>
+        <v>570310.5590055338</v>
       </c>
       <c r="H6" t="n">
-        <v>576943.1428270868</v>
+        <v>571874.1944034888</v>
       </c>
       <c r="I6" t="n">
-        <v>578402.7544666732</v>
+        <v>573440.0126618397</v>
       </c>
       <c r="J6" t="n">
-        <v>264344.4156695657</v>
+        <v>226455.7077578681</v>
       </c>
       <c r="K6" t="n">
-        <v>581328.1413927544</v>
+        <v>578991.4334810565</v>
       </c>
       <c r="L6" t="n">
-        <v>582793.9467915711</v>
+        <v>580457.2388798737</v>
       </c>
       <c r="M6" t="n">
-        <v>412789.6877655493</v>
+        <v>446599.8379524414</v>
       </c>
       <c r="N6" t="n">
-        <v>576002.5848004024</v>
+        <v>574260.7349872944</v>
       </c>
       <c r="O6" t="n">
-        <v>397970.3240581403</v>
+        <v>396228.4742450329</v>
       </c>
       <c r="P6" t="n">
-        <v>579940.9269091504</v>
+        <v>578199.0770960428</v>
       </c>
     </row>
   </sheetData>
@@ -26764,19 +26764,19 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J2" t="n">
         <v>225</v>
@@ -26868,19 +26868,19 @@
         <v>385</v>
       </c>
       <c r="E4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="F4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="G4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="H4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="I4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="J4" t="n">
         <v>1017</v>
@@ -26981,13 +26981,13 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,7 +26999,7 @@
         <v>225</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27008,7 +27008,7 @@
         <v>125</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>225</v>
@@ -27036,16 +27036,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
@@ -27082,10 +27082,10 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>632</v>
+        <v>531</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>486</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27213,7 +27213,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>632</v>
+        <v>531</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100.1429087359312</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>161.2819111235449</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>20.35776521751382</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
-      </c>
       <c r="U4" t="n">
-        <v>398.967459601631</v>
+        <v>277.5893585712976</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27657,7 +27657,7 @@
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>194.9855654067691</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>162.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>292.7160857525542</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>34.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,25 +27828,25 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C7" t="n">
         <v>400</v>
       </c>
-      <c r="C7" t="n">
-        <v>272.7252466480447</v>
-      </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>295.4906906887368</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>332.4263873262275</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
@@ -27888,10 +27888,10 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27970,7 +27970,7 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>371.2938086145854</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>184.7385553243522</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1819986780256</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28068,7 +28068,7 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28077,16 +28077,16 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>386.3757514961628</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H10" t="n">
         <v>400</v>
       </c>
-      <c r="H10" t="n">
-        <v>228.7711261016186</v>
-      </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28116,10 +28116,10 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28128,13 +28128,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>351.1274891438288</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28144,28 +28144,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I11" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,28 +28192,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y11" t="n">
-        <v>225</v>
+        <v>247.5890086145857</v>
       </c>
     </row>
     <row r="12">
@@ -28223,76 +28223,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P12" t="n">
-        <v>71.03760616835946</v>
+        <v>166.1982915220772</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>251</v>
       </c>
       <c r="R12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13">
@@ -28302,76 +28302,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
@@ -28381,28 +28381,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F14" t="n">
-        <v>219.5068074428801</v>
+        <v>251</v>
       </c>
       <c r="G14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>71.03760616835949</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>225</v>
+        <v>244.1190264315979</v>
       </c>
       <c r="O15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17">
@@ -28618,28 +28618,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G17" t="n">
-        <v>219.5068074428802</v>
+        <v>251</v>
       </c>
       <c r="H17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,28 +28666,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
@@ -28697,76 +28697,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I18" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
-        <v>225</v>
+        <v>26.99264054024948</v>
       </c>
       <c r="K18" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>19.11687125883913</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q18" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19">
@@ -28776,76 +28776,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20">
@@ -28855,28 +28855,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H20" t="n">
-        <v>219.5068074428801</v>
+        <v>251</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,28 +28903,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21">
@@ -28934,76 +28934,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>26.99048536749083</v>
+        <v>251</v>
       </c>
       <c r="P21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>225</v>
+        <v>200.0719056307292</v>
       </c>
       <c r="R21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22">
@@ -29013,76 +29013,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23">
@@ -29092,28 +29092,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I23" t="n">
-        <v>144.5879671255647</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,28 +29140,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24">
@@ -29171,76 +29171,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I24" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K24" t="n">
-        <v>19.11687125883913</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>26.99264054024968</v>
       </c>
       <c r="O24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25">
@@ -29250,76 +29250,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26">
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="C26" t="n">
         <v>225</v>
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29444,16 +29444,16 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
+        <v>78.9112202770111</v>
+      </c>
+      <c r="O27" t="n">
         <v>225</v>
-      </c>
-      <c r="O27" t="n">
-        <v>26.99048536749061</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
       </c>
       <c r="Q27" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
         <v>225</v>
@@ -29581,7 +29581,7 @@
         <v>225</v>
       </c>
       <c r="G29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="H29" t="n">
         <v>225</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S29" t="n">
         <v>225</v>
@@ -29669,13 +29669,13 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
-        <v>225</v>
+        <v>26.99048536749061</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>26.99048536749063</v>
+        <v>225</v>
       </c>
       <c r="M30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>225</v>
       </c>
       <c r="I32" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29869,7 +29869,7 @@
         <v>225</v>
       </c>
       <c r="X32" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="Y32" t="n">
         <v>225</v>
@@ -29903,19 +29903,19 @@
         <v>225</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J33" t="n">
         <v>225</v>
       </c>
       <c r="K33" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="L33" t="n">
         <v>225</v>
       </c>
       <c r="M33" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N33" t="n">
         <v>225</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30134,7 +30134,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30179,13 +30179,13 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30216,7 +30216,7 @@
         <v>350</v>
       </c>
       <c r="H37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="I37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30365,13 +30365,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>332.1680871864211</v>
@@ -30419,7 +30419,7 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>279.9943346964701</v>
+        <v>350</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
@@ -30593,10 +30593,10 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>350</v>
+      </c>
+      <c r="C42" t="n">
         <v>263.0617733495848</v>
-      </c>
-      <c r="C42" t="n">
-        <v>350</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,7 +30802,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30890,16 +30890,16 @@
         <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
       </c>
       <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
         <v>350</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="46">
@@ -34749,22 +34749,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N2" t="n">
         <v>385</v>
       </c>
       <c r="O2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>248.0090683271731</v>
+        <v>126.6309672968397</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34943,7 +34943,7 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34989,10 +34989,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>385.0000000000035</v>
       </c>
       <c r="N5" t="n">
-        <v>369.4444444444445</v>
+        <v>385.0000000000034</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>385</v>
+        <v>369.4444444444376</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,25 +35114,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>14.50978585178027</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>103.6552612246088</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
@@ -35174,10 +35174,10 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35226,7 +35226,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>385</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="N8" t="n">
         <v>385</v>
@@ -35354,7 +35354,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35363,16 +35363,16 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>111.9928955284208</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
         <v>249.0416087255421</v>
@@ -35414,13 +35414,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>124.7546793051191</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>295.7499460170249</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>962.6692363858147</v>
+        <v>285.5327895502034</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,31 +35530,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N12" t="n">
-        <v>359.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>184.7036106830127</v>
+        <v>279.8642960367304</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35603,16 +35603,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I13" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J13" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -35642,19 +35642,19 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U13" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>705.2756440294895</v>
       </c>
       <c r="L14" t="n">
-        <v>373.6502353900541</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>962.6692363858147</v>
+        <v>916</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,28 +35767,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>7.873614108651466</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>196.2462124060352</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>416.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>499.091375348687</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>359.6265501086548</v>
+        <v>378.7455765402527</v>
       </c>
       <c r="O15" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35840,16 +35840,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I16" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J16" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35879,19 +35879,19 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U16" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V16" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>415.6620101977433</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,10 +35943,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>962.6692363858147</v>
+        <v>916</v>
       </c>
       <c r="P17" t="n">
-        <v>373.6502353900542</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36004,31 +36004,31 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>350.2086062376757</v>
+        <v>152.2012467779252</v>
       </c>
       <c r="K18" t="n">
-        <v>416.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>293.2082466075261</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>359.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>338.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36077,16 +36077,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I19" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J19" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -36116,19 +36116,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U19" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -36168,25 +36168,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230996</v>
+        <v>529.437296015391</v>
       </c>
       <c r="L20" t="n">
-        <v>916.1914086561842</v>
+        <v>916</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>420.1280631196846</v>
+        <v>916</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,28 +36244,28 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>416.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>499.091375348687</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>359.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>268.4475072702372</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>51.92073490952041</v>
+        <v>26.99264054024963</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36314,16 +36314,16 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I22" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J22" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -36353,19 +36353,19 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U22" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V22" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>215.3137198726095</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>916</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>962.6692363858147</v>
+        <v>916</v>
       </c>
       <c r="P23" t="n">
-        <v>870.2908726334418</v>
+        <v>216.5371277208427</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,31 +36478,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>210.2207258996305</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>499.091375348687</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>359.6265501086548</v>
+        <v>161.6191906489045</v>
       </c>
       <c r="O24" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>338.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36551,16 +36551,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I25" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J25" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -36590,19 +36590,19 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U25" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>815.3897934607513</v>
+        <v>466.0285991424272</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36730,16 +36730,16 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>213.5377703856659</v>
       </c>
       <c r="O27" t="n">
-        <v>268.4475072702369</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>916.1914086561842</v>
@@ -36888,16 +36888,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>44.87353780253611</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>962.6692363858147</v>
+        <v>266.7123080093424</v>
       </c>
       <c r="P29" t="n">
         <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,13 +36955,13 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>350.2086062376757</v>
+        <v>152.1990916051663</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>301.0818607161776</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
         <v>311.9500421645043</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37131,10 +37131,10 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P32" t="n">
-        <v>816.6796243321426</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>341.6504820397668</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,19 +37189,19 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>218.0943400082819</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N33" t="n">
         <v>359.6265501086548</v>
@@ -37359,19 +37359,19 @@
         <v>559.0000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="P35" t="n">
-        <v>536.4141414141411</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H37" t="n">
-        <v>121.2288738983814</v>
+        <v>113.4402045325156</v>
       </c>
       <c r="I37" t="n">
         <v>173.3665443798817</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>93.38475247205298</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37827,25 +37827,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>20.40522350612654</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
